--- a/input/mapping/062. OCB_GOLD_TCKH_WORKING_DAY_BAOANH.xlsx
+++ b/input/mapping/062. OCB_GOLD_TCKH_WORKING_DAY_BAOANH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1704" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F841EABC-79A3-4F18-B903-633A1949B295}"/>
+  <xr:revisionPtr revIDLastSave="1716" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8DEA8EC-7D4F-4B18-A554-547F0BC6AF82}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -120,7 +120,15 @@
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE OR REPLACE TABLE working_day AS
+INSERT OVERWRITE working_day (
+    DATA_DT,
+    FROM_DATE_DT,
+    FROM_DT,
+    END_DT,
+    END_DATE_DT,
+    BEGIN_OF_MONTH,
+    BEGIN_OF_MONTH_DATE
+)
 WITH
 v_from_dt AS (
     SELECT
@@ -2561,7 +2569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="254">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3248,6 +3256,9 @@
     </xf>
     <xf numFmtId="0" fontId="43" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" indent="1"/>
@@ -3767,48 +3778,48 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" s="118"/>
-      <c r="B12" s="243" t="s">
+      <c r="B12" s="244" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="244"/>
-      <c r="D12" s="244"/>
-      <c r="E12" s="244"/>
+      <c r="C12" s="245"/>
+      <c r="D12" s="245"/>
+      <c r="E12" s="245"/>
     </row>
     <row r="13" spans="1:48">
       <c r="A13" s="119"/>
-      <c r="B13" s="243" t="s">
+      <c r="B13" s="244" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="244"/>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
+      <c r="C13" s="245"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="245"/>
     </row>
     <row r="14" spans="1:48">
       <c r="A14" s="120"/>
-      <c r="B14" s="243" t="s">
+      <c r="B14" s="244" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="244"/>
-      <c r="D14" s="244"/>
-      <c r="E14" s="244"/>
+      <c r="C14" s="245"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
     </row>
     <row r="15" spans="1:48">
       <c r="A15" s="121"/>
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="244" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="244"/>
-      <c r="D15" s="244"/>
-      <c r="E15" s="244"/>
+      <c r="C15" s="245"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
     </row>
     <row r="16" spans="1:48">
       <c r="A16" s="122"/>
-      <c r="B16" s="243" t="s">
+      <c r="B16" s="244" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="244"/>
-      <c r="D16" s="244"/>
-      <c r="E16" s="244"/>
+      <c r="C16" s="245"/>
+      <c r="D16" s="245"/>
+      <c r="E16" s="245"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="123" t="s">
@@ -7610,7 +7621,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="409.6">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -7618,7 +7629,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="133"/>
-      <c r="D3" t="s">
+      <c r="D3" s="243" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7652,7 +7663,7 @@
       <c r="E1" s="182"/>
       <c r="F1" s="182"/>
       <c r="G1" s="183"/>
-      <c r="H1" s="245"/>
+      <c r="H1" s="246"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="93" t="s">
@@ -7672,7 +7683,7 @@
       </c>
       <c r="F2" s="182"/>
       <c r="G2" s="184"/>
-      <c r="H2" s="245"/>
+      <c r="H2" s="246"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="90">
@@ -7690,7 +7701,7 @@
       <c r="E3" s="185"/>
       <c r="F3" s="185"/>
       <c r="G3" s="186"/>
-      <c r="H3" s="245"/>
+      <c r="H3" s="246"/>
     </row>
     <row r="4" spans="1:8" ht="64.5" customHeight="1">
       <c r="A4" s="90">
@@ -7710,7 +7721,7 @@
       </c>
       <c r="F4" s="185"/>
       <c r="G4" s="186"/>
-      <c r="H4" s="245"/>
+      <c r="H4" s="246"/>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
       <c r="A5" s="187" t="s">
@@ -7722,7 +7733,7 @@
       <c r="E5" s="188"/>
       <c r="F5" s="188"/>
       <c r="G5" s="189"/>
-      <c r="H5" s="245"/>
+      <c r="H5" s="246"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="93" t="s">
@@ -7746,7 +7757,7 @@
       <c r="G6" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="245"/>
+      <c r="H6" s="246"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="90">
@@ -7770,7 +7781,7 @@
       <c r="G7" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="245"/>
+      <c r="H7" s="246"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="90">
@@ -7794,7 +7805,7 @@
       <c r="G8" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="245"/>
+      <c r="H8" s="246"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="90">
@@ -7818,7 +7829,7 @@
       <c r="G9" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="245"/>
+      <c r="H9" s="246"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="90">
@@ -7842,7 +7853,7 @@
       <c r="G10" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H10" s="245"/>
+      <c r="H10" s="246"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="90">
@@ -7866,7 +7877,7 @@
       <c r="G11" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H11" s="245"/>
+      <c r="H11" s="246"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="90">
@@ -7890,7 +7901,7 @@
       <c r="G12" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="245"/>
+      <c r="H12" s="246"/>
     </row>
     <row r="13" spans="1:8" ht="60.75">
       <c r="A13" s="90">
@@ -7914,7 +7925,7 @@
       <c r="G13" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="H13" s="245"/>
+      <c r="H13" s="246"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="90">
@@ -7938,7 +7949,7 @@
       <c r="G14" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="245"/>
+      <c r="H14" s="246"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="90">
@@ -7962,7 +7973,7 @@
       <c r="G15" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="245"/>
+      <c r="H15" s="246"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="90">
@@ -7986,7 +7997,7 @@
       <c r="G16" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="245"/>
+      <c r="H16" s="246"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="90">
@@ -8010,7 +8021,7 @@
       <c r="G17" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H17" s="245"/>
+      <c r="H17" s="246"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="90">
@@ -8034,7 +8045,7 @@
       <c r="G18" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H18" s="245"/>
+      <c r="H18" s="246"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="90">
@@ -8058,7 +8069,7 @@
       <c r="G19" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H19" s="245"/>
+      <c r="H19" s="246"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="90">
@@ -8082,7 +8093,7 @@
       <c r="G20" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H20" s="245"/>
+      <c r="H20" s="246"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="90">
@@ -8106,7 +8117,7 @@
       <c r="G21" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="245"/>
+      <c r="H21" s="246"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="90">
@@ -8130,7 +8141,7 @@
       <c r="G22" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H22" s="245"/>
+      <c r="H22" s="246"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="90">
@@ -8154,7 +8165,7 @@
       <c r="G23" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H23" s="245"/>
+      <c r="H23" s="246"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="90">
@@ -8178,7 +8189,7 @@
       <c r="G24" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H24" s="245"/>
+      <c r="H24" s="246"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="90">
@@ -8202,7 +8213,7 @@
       <c r="G25" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H25" s="245"/>
+      <c r="H25" s="246"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="90">
@@ -8226,7 +8237,7 @@
       <c r="G26" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H26" s="245"/>
+      <c r="H26" s="246"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="90">
@@ -8250,7 +8261,7 @@
       <c r="G27" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H27" s="245"/>
+      <c r="H27" s="246"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="90">
@@ -8274,7 +8285,7 @@
       <c r="G28" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H28" s="245"/>
+      <c r="H28" s="246"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="90">
@@ -8298,7 +8309,7 @@
       <c r="G29" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H29" s="245"/>
+      <c r="H29" s="246"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="90">
@@ -8322,7 +8333,7 @@
       <c r="G30" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H30" s="245"/>
+      <c r="H30" s="246"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="90">
@@ -8346,7 +8357,7 @@
       <c r="G31" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H31" s="245"/>
+      <c r="H31" s="246"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="90">
@@ -8370,7 +8381,7 @@
       <c r="G32" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H32" s="245"/>
+      <c r="H32" s="246"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="90">
@@ -8394,7 +8405,7 @@
       <c r="G33" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H33" s="245"/>
+      <c r="H33" s="246"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="90">
@@ -8418,7 +8429,7 @@
       <c r="G34" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H34" s="245"/>
+      <c r="H34" s="246"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="90">
@@ -8442,7 +8453,7 @@
       <c r="G35" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H35" s="245"/>
+      <c r="H35" s="246"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="90">
@@ -8466,7 +8477,7 @@
       <c r="G36" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H36" s="245"/>
+      <c r="H36" s="246"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="90">
@@ -8490,7 +8501,7 @@
       <c r="G37" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H37" s="245"/>
+      <c r="H37" s="246"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="90">
@@ -8514,7 +8525,7 @@
       <c r="G38" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H38" s="245"/>
+      <c r="H38" s="246"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="90">
@@ -8538,7 +8549,7 @@
       <c r="G39" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H39" s="245"/>
+      <c r="H39" s="246"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="90">
@@ -8562,7 +8573,7 @@
       <c r="G40" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H40" s="245"/>
+      <c r="H40" s="246"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="90">
@@ -8586,7 +8597,7 @@
       <c r="G41" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H41" s="245"/>
+      <c r="H41" s="246"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="90">
@@ -8610,7 +8621,7 @@
       <c r="G42" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="245"/>
+      <c r="H42" s="246"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="90">
@@ -8634,7 +8645,7 @@
       <c r="G43" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H43" s="245"/>
+      <c r="H43" s="246"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="90">
@@ -8658,7 +8669,7 @@
       <c r="G44" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H44" s="245"/>
+      <c r="H44" s="246"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="90">
@@ -8682,7 +8693,7 @@
       <c r="G45" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H45" s="245"/>
+      <c r="H45" s="246"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="90">
@@ -8706,7 +8717,7 @@
       <c r="G46" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H46" s="245"/>
+      <c r="H46" s="246"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="90">
@@ -8730,7 +8741,7 @@
       <c r="G47" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H47" s="245"/>
+      <c r="H47" s="246"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="90">
@@ -8754,7 +8765,7 @@
       <c r="G48" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H48" s="245"/>
+      <c r="H48" s="246"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="90">
@@ -8778,7 +8789,7 @@
       <c r="G49" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H49" s="245"/>
+      <c r="H49" s="246"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="90">
@@ -8802,7 +8813,7 @@
       <c r="G50" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H50" s="245"/>
+      <c r="H50" s="246"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="90">
@@ -8826,7 +8837,7 @@
       <c r="G51" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H51" s="245"/>
+      <c r="H51" s="246"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="90">
@@ -8850,7 +8861,7 @@
       <c r="G52" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="245"/>
+      <c r="H52" s="246"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="90">
@@ -8874,7 +8885,7 @@
       <c r="G53" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H53" s="245"/>
+      <c r="H53" s="246"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="90">
@@ -8898,7 +8909,7 @@
       <c r="G54" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H54" s="245"/>
+      <c r="H54" s="246"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="90">
@@ -8922,7 +8933,7 @@
       <c r="G55" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H55" s="245"/>
+      <c r="H55" s="246"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="90">
@@ -8946,7 +8957,7 @@
       <c r="G56" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H56" s="245"/>
+      <c r="H56" s="246"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="90">
@@ -8970,7 +8981,7 @@
       <c r="G57" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="H57" s="245"/>
+      <c r="H57" s="246"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="114">
@@ -8994,137 +9005,137 @@
       <c r="G58" s="115" t="s">
         <v>45</v>
       </c>
-      <c r="H58" s="245"/>
+      <c r="H58" s="246"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="246">
+      <c r="A59" s="247">
         <v>53</v>
       </c>
-      <c r="B59" s="247" t="s">
+      <c r="B59" s="248" t="s">
         <v>40</v>
       </c>
-      <c r="C59" s="248" t="s">
+      <c r="C59" s="249" t="s">
         <v>153</v>
       </c>
-      <c r="D59" s="249" t="s">
+      <c r="D59" s="250" t="s">
         <v>42</v>
       </c>
-      <c r="E59" s="250" t="s">
-        <v>43</v>
-      </c>
-      <c r="F59" s="247" t="s">
+      <c r="E59" s="251" t="s">
+        <v>43</v>
+      </c>
+      <c r="F59" s="248" t="s">
         <v>154</v>
       </c>
-      <c r="G59" s="247" t="s">
+      <c r="G59" s="248" t="s">
         <v>45</v>
       </c>
-      <c r="H59" s="245"/>
+      <c r="H59" s="246"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="246">
+      <c r="A60" s="247">
         <v>54</v>
       </c>
-      <c r="B60" s="247" t="s">
+      <c r="B60" s="248" t="s">
         <v>40</v>
       </c>
-      <c r="C60" s="248" t="s">
+      <c r="C60" s="249" t="s">
         <v>155</v>
       </c>
-      <c r="D60" s="249" t="s">
+      <c r="D60" s="250" t="s">
         <v>42</v>
       </c>
-      <c r="E60" s="250" t="s">
-        <v>43</v>
-      </c>
-      <c r="F60" s="247" t="s">
+      <c r="E60" s="251" t="s">
+        <v>43</v>
+      </c>
+      <c r="F60" s="248" t="s">
         <v>156</v>
       </c>
-      <c r="G60" s="247" t="s">
+      <c r="G60" s="248" t="s">
         <v>45</v>
       </c>
-      <c r="H60" s="245"/>
+      <c r="H60" s="246"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="246">
+      <c r="A61" s="247">
         <v>55</v>
       </c>
-      <c r="B61" s="247" t="s">
+      <c r="B61" s="248" t="s">
         <v>40</v>
       </c>
-      <c r="C61" s="248" t="s">
+      <c r="C61" s="249" t="s">
         <v>157</v>
       </c>
-      <c r="D61" s="249" t="s">
+      <c r="D61" s="250" t="s">
         <v>42</v>
       </c>
-      <c r="E61" s="250" t="s">
-        <v>43</v>
-      </c>
-      <c r="F61" s="247" t="s">
+      <c r="E61" s="251" t="s">
+        <v>43</v>
+      </c>
+      <c r="F61" s="248" t="s">
         <v>158</v>
       </c>
-      <c r="G61" s="247" t="s">
+      <c r="G61" s="248" t="s">
         <v>45</v>
       </c>
-      <c r="H61" s="245"/>
+      <c r="H61" s="246"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="246">
+      <c r="A62" s="247">
         <v>56</v>
       </c>
-      <c r="B62" s="247" t="s">
+      <c r="B62" s="248" t="s">
         <v>40</v>
       </c>
-      <c r="C62" s="248" t="s">
+      <c r="C62" s="249" t="s">
         <v>159</v>
       </c>
-      <c r="D62" s="249" t="s">
+      <c r="D62" s="250" t="s">
         <v>75</v>
       </c>
-      <c r="E62" s="250" t="s">
-        <v>43</v>
-      </c>
-      <c r="F62" s="247" t="s">
+      <c r="E62" s="251" t="s">
+        <v>43</v>
+      </c>
+      <c r="F62" s="248" t="s">
         <v>160</v>
       </c>
-      <c r="G62" s="247" t="s">
+      <c r="G62" s="248" t="s">
         <v>45</v>
       </c>
-      <c r="H62" s="245"/>
+      <c r="H62" s="246"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="246">
+      <c r="A63" s="247">
         <v>57</v>
       </c>
-      <c r="B63" s="247" t="s">
+      <c r="B63" s="248" t="s">
         <v>40</v>
       </c>
-      <c r="C63" s="248" t="s">
+      <c r="C63" s="249" t="s">
         <v>161</v>
       </c>
-      <c r="D63" s="249" t="s">
+      <c r="D63" s="250" t="s">
         <v>42</v>
       </c>
-      <c r="E63" s="250" t="s">
-        <v>43</v>
-      </c>
-      <c r="F63" s="247" t="s">
+      <c r="E63" s="251" t="s">
+        <v>43</v>
+      </c>
+      <c r="F63" s="248" t="s">
         <v>162</v>
       </c>
-      <c r="G63" s="247" t="s">
+      <c r="G63" s="248" t="s">
         <v>45</v>
       </c>
-      <c r="H63" s="245"/>
+      <c r="H63" s="246"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="251"/>
-      <c r="B64" s="245"/>
-      <c r="C64" s="251"/>
-      <c r="D64" s="251"/>
-      <c r="E64" s="245"/>
-      <c r="F64" s="245"/>
-      <c r="G64" s="245"/>
-      <c r="H64" s="252"/>
+      <c r="A64" s="252"/>
+      <c r="B64" s="246"/>
+      <c r="C64" s="252"/>
+      <c r="D64" s="252"/>
+      <c r="E64" s="246"/>
+      <c r="F64" s="246"/>
+      <c r="G64" s="246"/>
+      <c r="H64" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9418,12 +9429,12 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A5" s="252"/>
-      <c r="B5" s="252"/>
-      <c r="C5" s="252"/>
-      <c r="D5" s="252"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
+      <c r="A5" s="253"/>
+      <c r="B5" s="253"/>
+      <c r="C5" s="253"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="198" t="s">
@@ -9433,7 +9444,7 @@
       <c r="C7" s="204"/>
       <c r="D7" s="204"/>
       <c r="E7" s="204"/>
-      <c r="F7" s="252"/>
+      <c r="F7" s="253"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="46" t="s">
@@ -9451,7 +9462,7 @@
       <c r="E8" s="46" t="s">
         <v>173</v>
       </c>
-      <c r="F8" s="252"/>
+      <c r="F8" s="253"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="51" t="s">
@@ -9469,7 +9480,7 @@
       <c r="E9" s="54" t="s">
         <v>194</v>
       </c>
-      <c r="F9" s="252"/>
+      <c r="F9" s="253"/>
     </row>
     <row r="10" spans="1:6" ht="60.75">
       <c r="A10" s="51" t="s">
@@ -9487,7 +9498,7 @@
       <c r="E10" s="54" t="s">
         <v>196</v>
       </c>
-      <c r="F10" s="252"/>
+      <c r="F10" s="253"/>
     </row>
     <row r="11" spans="1:6" ht="91.5">
       <c r="A11" s="51" t="s">
@@ -9505,7 +9516,7 @@
       <c r="E11" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="F11" s="252"/>
+      <c r="F11" s="253"/>
     </row>
     <row r="12" spans="1:6" ht="121.5">
       <c r="A12" s="51" t="s">
@@ -9523,7 +9534,7 @@
       <c r="E12" s="54" t="s">
         <v>202</v>
       </c>
-      <c r="F12" s="252"/>
+      <c r="F12" s="253"/>
     </row>
     <row r="13" spans="1:6" ht="76.5">
       <c r="A13" s="51" t="s">
@@ -9541,7 +9552,7 @@
       <c r="E13" s="54" t="s">
         <v>204</v>
       </c>
-      <c r="F13" s="252"/>
+      <c r="F13" s="253"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="51" t="s">
@@ -9559,7 +9570,7 @@
       <c r="E14" s="54" t="s">
         <v>207</v>
       </c>
-      <c r="F14" s="252"/>
+      <c r="F14" s="253"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="51" t="s">
@@ -9577,7 +9588,7 @@
       <c r="E15" s="54" t="s">
         <v>209</v>
       </c>
-      <c r="F15" s="252"/>
+      <c r="F15" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -12409,6 +12420,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -12580,33 +12610,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
 </file>